--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -63,29 +63,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>BRAKE</t>
   </si>
   <si>
-    <t>ブレーキをかける</t>
+    <t>ブレーキ</t>
   </si>
   <si>
     <t>ENGINE</t>
   </si>
   <si>
-    <t>エンジン台</t>
+    <t>エンジン</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>ゲームオーバー</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>戻る</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -119,13 +122,13 @@
     <t>MenuUIForm.Tips</t>
   </si>
   <si>
-    <t>クリックして開始</t>
+    <t>タップして開始</t>
   </si>
   <si>
     <t>Nothing</t>
   </si>
   <si>
-    <t>実装されていません</t>
+    <t>未実装</t>
   </si>
   <si>
     <t>OFF</t>
@@ -137,7 +140,7 @@
     <t>ON</t>
   </si>
   <si>
-    <t>開く</t>
+    <t>オン</t>
   </si>
   <si>
     <t>RatingDialog.CancelTxt</t>
@@ -149,25 +152,37 @@
     <t>RatingDialog.Description</t>
   </si>
   <si>
-    <t>このゲームは好きですか。\n 5つ星を評価してください！</t>
+    <t>このゲームはお好きですか？\n5つ星の評価をお願いします！</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
-    <t>ご肯定ありがとうございます！私たちはもっと頑張ります！</t>
+    <t>ご高評価いただきありがとうございます！これからも頑張ります！</t>
   </si>
   <si>
     <t>RatingDialog.LowRatingTips</t>
   </si>
   <si>
-    <t>あなたの評価に感謝して、私たちは全力を尽くして最適化を改善します！</t>
+    <t>ご評価ありがとうございます、改善に努めます！</t>
   </si>
   <si>
     <t>RatingDialog.RateTxt</t>
   </si>
   <si>
-    <t>スター人</t>
+    <t>評価</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>ショップ</t>
+  </si>
+  <si>
+    <t>STEERING</t>
+  </si>
+  <si>
+    <t>ステアリング</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -185,64 +200,52 @@
     <t>Settings.Music</t>
   </si>
   <si>
-    <t>バックミュージック</t>
+    <t>BGM</t>
   </si>
   <si>
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>プライバシー契約</t>
+    <t>プライバシーポリシー</t>
   </si>
   <si>
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>評価</t>
-  </si>
-  <si>
     <t>Settings.SFX</t>
   </si>
   <si>
-    <t>サウンドエフェクト</t>
+    <t>効果音</t>
   </si>
   <si>
     <t>Settings.Title</t>
   </si>
   <si>
-    <t>設定＃セッテイ＃</t>
+    <t>設定</t>
   </si>
   <si>
     <t>Settings.Vibrate</t>
   </si>
   <si>
-    <t>ぎょっとさせる</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>店</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
-    <t>ドライブ</t>
+    <t>バイブレーション</t>
   </si>
   <si>
     <t>TermsOfService</t>
   </si>
   <si>
-    <t>サービス条件</t>
+    <t>利用規約</t>
   </si>
   <si>
     <t>UNLOCK</t>
   </si>
   <si>
-    <t>ロック解除</t>
+    <t>アンロック</t>
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>ゲームクリア</t>
   </si>
 </sst>
 </file>
@@ -424,6 +427,130 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -3997,196 +4124,196 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -4240,7 +4367,7 @@
         <v>59</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4255,7 +4382,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId150" name="A1">
+            <control shapeId="1056" r:id="rId180" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4277,7 +4404,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId151" name="A2">
+            <control shapeId="1057" r:id="rId181" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4299,7 +4426,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId152" name="A3">
+            <control shapeId="1058" r:id="rId182" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4321,7 +4448,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId153" name="A4">
+            <control shapeId="1059" r:id="rId183" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4343,7 +4470,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId154" name="A5">
+            <control shapeId="1060" r:id="rId184" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4365,7 +4492,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId155" name="A6">
+            <control shapeId="1061" r:id="rId185" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4387,7 +4514,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId156" name="A7">
+            <control shapeId="1062" r:id="rId186" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4409,7 +4536,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId157" name="A8">
+            <control shapeId="1063" r:id="rId187" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4431,7 +4558,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId158" name="A9">
+            <control shapeId="1064" r:id="rId188" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4453,7 +4580,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId159" name="A10">
+            <control shapeId="1065" r:id="rId189" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4475,7 +4602,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId160" name="A11">
+            <control shapeId="1066" r:id="rId190" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4497,7 +4624,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId161" name="A12">
+            <control shapeId="1067" r:id="rId191" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4519,7 +4646,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId162" name="A13">
+            <control shapeId="1068" r:id="rId192" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4541,7 +4668,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId163" name="A14">
+            <control shapeId="1069" r:id="rId193" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4563,7 +4690,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId164" name="A15">
+            <control shapeId="1070" r:id="rId194" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4585,7 +4712,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId165" name="A16">
+            <control shapeId="1071" r:id="rId195" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4607,7 +4734,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId166" name="A17">
+            <control shapeId="1072" r:id="rId196" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4629,7 +4756,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId167" name="A18">
+            <control shapeId="1073" r:id="rId197" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4651,7 +4778,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId168" name="A19">
+            <control shapeId="1074" r:id="rId198" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4673,7 +4800,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId169" name="A20">
+            <control shapeId="1075" r:id="rId199" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4695,7 +4822,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId170" name="A21">
+            <control shapeId="1076" r:id="rId200" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4717,7 +4844,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId171" name="A22">
+            <control shapeId="1077" r:id="rId201" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4739,7 +4866,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId172" name="A23">
+            <control shapeId="1078" r:id="rId202" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4761,7 +4888,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId173" name="A24">
+            <control shapeId="1079" r:id="rId203" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4783,7 +4910,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId174" name="A25">
+            <control shapeId="1080" r:id="rId204" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4805,7 +4932,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId175" name="A26">
+            <control shapeId="1081" r:id="rId205" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4827,7 +4954,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId176" name="A27">
+            <control shapeId="1082" r:id="rId206" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4849,7 +4976,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId177" name="A28">
+            <control shapeId="1083" r:id="rId207" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4871,7 +4998,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId178" name="A29">
+            <control shapeId="1084" r:id="rId208" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4893,7 +5020,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId179" name="A30">
+            <control shapeId="1085" r:id="rId209" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4915,7 +5042,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId180" name="A31">
+            <control shapeId="1086" r:id="rId210" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
